--- a/ISA/dual_momentum_isa/old/DualMomentum_ISA_Alt3_2026-01.xlsx
+++ b/ISA/dual_momentum_isa/old/DualMomentum_ISA_Alt3_2026-01.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공격모드 ON: 합성(20.34%)이 SPY(17.72%) 및 BIL보다 우위</t>
+          <t>공격모드 ON: 합성(24.55%)이 SPY(15.87%) 및 BIL보다 우위</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.1771905919808086</v>
+        <v>0.1586914655204876</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.2033928024046168</v>
+        <v>0.2454909589936209</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.04147098911561975</v>
+        <v>0.04022364027895775</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
